--- a/AAII_Financials/Yearly/AWK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AWK_YR_FIN.xlsx
@@ -2972,10 +2972,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3075000</v>
+        <v>3078000</v>
       </c>
       <c r="E58" s="3">
-        <v>1527000</v>
+        <v>1516000</v>
       </c>
       <c r="F58" s="3">
         <v>654000</v>
@@ -3176,10 +3176,10 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2017000</v>
+        <v>1998000</v>
       </c>
       <c r="E62" s="3">
-        <v>2076000</v>
+        <v>2062000</v>
       </c>
       <c r="F62" s="3">
         <v>2029000</v>
